--- a/dataOrg.xlsx
+++ b/dataOrg.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\GitHub\ZelanoLabScripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B440897-29E2-41F9-A64F-4A72CAB965AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29901AE-8995-4CD9-BCFA-24AC70CF8B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-324" yWindow="648" windowWidth="18072" windowHeight="14004" xr2:uid="{557E2B97-4CE1-42B9-AC1F-F00B9E7AA925}"/>
+    <workbookView xWindow="588" yWindow="1800" windowWidth="18444" windowHeight="14532" xr2:uid="{557E2B97-4CE1-42B9-AC1F-F00B9E7AA925}"/>
   </bookViews>
   <sheets>
     <sheet name="outDat" sheetId="1" r:id="rId1"/>
-    <sheet name="BehDat_breathing" sheetId="4" r:id="rId2"/>
-    <sheet name="BehDat_O15" sheetId="5" r:id="rId3"/>
-    <sheet name="BehDat_cueTask" sheetId="2" r:id="rId4"/>
-    <sheet name="chanDat" sheetId="3" r:id="rId5"/>
+    <sheet name="breathing" sheetId="4" r:id="rId2"/>
+    <sheet name="O15" sheetId="5" r:id="rId3"/>
+    <sheet name="cueTask" sheetId="2" r:id="rId4"/>
+    <sheet name="Thresh" sheetId="6" r:id="rId5"/>
+    <sheet name="chanDat" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="204">
   <si>
     <t>Fields</t>
   </si>
@@ -261,9 +262,6 @@
     <t>"cr", "miss", "hit", "fa", "skip"</t>
   </si>
   <si>
-    <t>cueTask</t>
-  </si>
-  <si>
     <t>the actual data</t>
   </si>
   <si>
@@ -354,9 +352,6 @@
     <t>table: channels X vars</t>
   </si>
   <si>
-    <t>breathing</t>
-  </si>
-  <si>
     <t>heartBeats</t>
   </si>
   <si>
@@ -549,9 +544,6 @@
     <t>table</t>
   </si>
   <si>
-    <t>O15</t>
-  </si>
-  <si>
     <t>trial index</t>
   </si>
   <si>
@@ -589,6 +581,78 @@
   </si>
   <si>
     <t>1=correct .5=kinda 0=wrong</t>
+  </si>
+  <si>
+    <t>TTL</t>
+  </si>
+  <si>
+    <t>table of trials X event markers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTL struct: </t>
+  </si>
+  <si>
+    <t>trialStart</t>
+  </si>
+  <si>
+    <t>sniff</t>
+  </si>
+  <si>
+    <t>idx of TTL indicating trial start</t>
+  </si>
+  <si>
+    <t>idx of TTL indicating response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idx of sniff onset within trial </t>
+  </si>
+  <si>
+    <t>rows = trials</t>
+  </si>
+  <si>
+    <t>ConfirmSniff</t>
+  </si>
+  <si>
+    <t>freeSniff1</t>
+  </si>
+  <si>
+    <t>idx of first sniff (cued not free)</t>
+  </si>
+  <si>
+    <t>freeSniff2</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>freeSniff17</t>
+  </si>
+  <si>
+    <t>idx of free sniff TTL</t>
+  </si>
+  <si>
+    <t>cueTask_makeOutDat.m</t>
+  </si>
+  <si>
+    <t>breathingTaskPreProc_main.m</t>
+  </si>
+  <si>
+    <t>breathingTask_makeOutDat.m</t>
+  </si>
+  <si>
+    <t>cueTaskPreProc_main.m</t>
+  </si>
+  <si>
+    <t>1; raw emotion ratings; see tidyDataImport_closedLoopResp.R</t>
+  </si>
+  <si>
+    <t>O15PreProc_main.m</t>
+  </si>
+  <si>
+    <t>threshPreProc_makeOutDat.m</t>
+  </si>
+  <si>
+    <t>1; raw import</t>
   </si>
 </sst>
 </file>
@@ -961,15 +1025,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABBDA707-B96B-46AD-B156-1E086F68BE9C}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
     <col min="2" max="2" width="82.33203125" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.21875" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -980,16 +1050,25 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="F1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+      <c r="G1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1008,13 +1087,22 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" t="s">
         <v>88</v>
-      </c>
-      <c r="B3" t="s">
-        <v>89</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -1028,8 +1116,17 @@
       <c r="F3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1048,10 +1145,19 @@
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -1068,8 +1174,17 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1085,20 +1200,29 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
       </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
       <c r="D7">
         <v>1</v>
       </c>
@@ -1108,48 +1232,57 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
         <v>91</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>92</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>93</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -1168,8 +1301,17 @@
       <c r="F10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -1188,8 +1330,17 @@
       <c r="F11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1208,8 +1359,17 @@
       <c r="F12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1228,8 +1388,17 @@
       <c r="F13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1248,50 +1417,59 @@
       <c r="F14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
         <v>95</v>
-      </c>
-      <c r="B15" t="s">
-        <v>96</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -1299,39 +1477,39 @@
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
         <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>99</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -1339,17 +1517,17 @@
       <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1359,37 +1537,37 @@
       <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
         <v>101</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>102</v>
       </c>
-      <c r="C21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1399,17 +1577,17 @@
       <c r="C22" t="s">
         <v>32</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1419,17 +1597,17 @@
       <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -1439,41 +1617,71 @@
       <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
+      <c r="D24" s="1"/>
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" t="s">
         <v>105</v>
       </c>
-      <c r="B25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="C27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" t="s">
         <v>166</v>
       </c>
-      <c r="B26" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" t="s">
-        <v>168</v>
-      </c>
-      <c r="E26">
+      <c r="G28">
         <v>1</v>
       </c>
     </row>
@@ -1508,24 +1716,24 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
@@ -1533,24 +1741,24 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
@@ -1558,10 +1766,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
         <v>68</v>
@@ -1569,10 +1777,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
@@ -1580,10 +1788,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
         <v>68</v>
@@ -1591,10 +1799,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -1602,10 +1810,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
         <v>68</v>
@@ -1613,10 +1821,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
         <v>68</v>
@@ -1624,10 +1832,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
         <v>68</v>
@@ -1635,10 +1843,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -1646,10 +1854,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1660,57 +1868,57 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" t="s">
         <v>153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
         <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
         <v>68</v>
@@ -1718,10 +1926,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
         <v>68</v>
@@ -1729,10 +1937,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -1740,10 +1948,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
         <v>68</v>
@@ -1751,10 +1959,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
         <v>68</v>
@@ -1762,10 +1970,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -1773,10 +1981,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -1784,10 +1992,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
         <v>68</v>
@@ -1795,10 +2003,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
         <v>68</v>
@@ -1806,10 +2014,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C28" t="s">
         <v>68</v>
@@ -1817,10 +2025,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C29" t="s">
         <v>68</v>
@@ -1828,10 +2036,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
         <v>68</v>
@@ -1839,24 +2047,24 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
         <v>68</v>
@@ -1864,10 +2072,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
         <v>68</v>
@@ -1875,10 +2083,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
         <v>68</v>
@@ -1891,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9BD6D1-95EA-49C2-83D3-279C6F9488D0}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -1914,10 +2122,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
         <v>76</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -1928,7 +2136,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
@@ -1936,10 +2144,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
@@ -1947,10 +2155,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
         <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
@@ -1958,10 +2166,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
@@ -1969,24 +2177,24 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1994,32 +2202,32 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C10" t="s">
         <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -2027,12 +2235,97 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
         <v>82</v>
       </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
       <c r="C12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2043,11 +2336,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3107DCE1-7FA8-4129-900F-066694D51124}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2200,10 +2493,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
         <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -2211,10 +2504,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
         <v>78</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -2222,10 +2515,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
         <v>80</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -2233,12 +2526,53 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
         <v>82</v>
       </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
       <c r="C15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2248,6 +2582,230 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2730AC78-8EB2-4F72-85EF-47D5B60BB2CD}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="34.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE15F364-9821-41AB-BB49-0278F3A9E699}">
   <dimension ref="A2:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/dataOrg.xlsx
+++ b/dataOrg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\GitHub\ZelanoLabScripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29901AE-8995-4CD9-BCFA-24AC70CF8B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B34719-385D-49F4-8EA1-0520D2345867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="588" yWindow="1800" windowWidth="18444" windowHeight="14532" xr2:uid="{557E2B97-4CE1-42B9-AC1F-F00B9E7AA925}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{557E2B97-4CE1-42B9-AC1F-F00B9E7AA925}"/>
   </bookViews>
   <sheets>
     <sheet name="outDat" sheetId="1" r:id="rId1"/>
@@ -2809,6 +2809,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE15F364-9821-41AB-BB49-0278F3A9E699}">
   <dimension ref="A2:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
